--- a/BOM/Fob_Transmitter/eSpark_BOM_Fob_Transmitter.xlsx
+++ b/BOM/Fob_Transmitter/eSpark_BOM_Fob_Transmitter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\OliverStanton-WaterMonitor\BOM\Fob_Transmitter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C00387A-5EFD-40A1-9103-31A1FDC071B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3325A2C2-1FCA-4EB1-8471-942346E1F328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5280" yWindow="3345" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -296,12 +296,6 @@
     <t>C275404</t>
   </si>
   <si>
-    <t>C2829889</t>
-  </si>
-  <si>
-    <t>PH-00013</t>
-  </si>
-  <si>
     <t>C99782</t>
   </si>
   <si>
@@ -330,6 +324,13 @@
   </si>
   <si>
     <t>(Fob_Transmitter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ254V-11-02P
+</t>
+  </si>
+  <si>
+    <t>C492401</t>
   </si>
 </sst>
 </file>
@@ -809,25 +810,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -837,18 +838,18 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -863,7 +864,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -873,8 +874,8 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -886,45 +887,45 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -949,7 +950,7 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -996,6 +997,12 @@
     </xf>
     <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1029,11 +1036,8 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1411,15 +1415,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="69"/>
-      <c r="R1" s="69"/>
-      <c r="S1" s="70"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="72"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1430,7 +1434,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="52" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
@@ -1455,7 +1459,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="53" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
@@ -1469,7 +1473,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="71"/>
+      <c r="S3" s="73"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1480,7 +1484,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="54" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
@@ -1494,7 +1498,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="72"/>
+      <c r="S4" s="74"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1519,7 +1523,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="72"/>
+      <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1540,7 +1544,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="72"/>
+      <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1561,7 +1565,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="72"/>
+      <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1582,7 +1586,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="72"/>
+      <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1614,7 +1618,7 @@
         <v>65</v>
       </c>
       <c r="K9" s="56" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L9" s="30" t="s">
         <v>62</v>
@@ -1647,7 +1651,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="69" t="s">
         <v>73</v>
       </c>
       <c r="D10" s="46" t="s">
@@ -1703,7 +1707,7 @@
         <f t="shared" ref="B11:B19" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="80" t="s">
+      <c r="C11" s="70" t="s">
         <v>73</v>
       </c>
       <c r="D11" s="49" t="s">
@@ -1759,7 +1763,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="79" t="s">
+      <c r="C12" s="69" t="s">
         <v>73</v>
       </c>
       <c r="D12" s="46" t="s">
@@ -1815,7 +1819,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="80" t="s">
+      <c r="C13" s="70" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="49" t="s">
@@ -1871,14 +1875,14 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="79" t="s">
+      <c r="C14" s="69" t="s">
         <v>74</v>
       </c>
       <c r="D14" s="46" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F14" s="46" t="s">
         <v>32</v>
@@ -1927,7 +1931,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="80" t="s">
+      <c r="C15" s="70" t="s">
         <v>75</v>
       </c>
       <c r="D15" s="49" t="s">
@@ -1983,7 +1987,7 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="79" t="s">
+      <c r="C16" s="69" t="s">
         <v>74</v>
       </c>
       <c r="D16" s="46" t="s">
@@ -1998,14 +2002,14 @@
       <c r="G16" s="62">
         <v>61300211121</v>
       </c>
-      <c r="H16" s="46" t="s">
-        <v>89</v>
+      <c r="H16" s="81" t="s">
+        <v>98</v>
       </c>
       <c r="I16" s="46" t="s">
         <v>54</v>
       </c>
       <c r="J16" s="46" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="K16" s="47" t="s">
         <v>80</v>
@@ -2024,11 +2028,11 @@
         <v>82</v>
       </c>
       <c r="P16" s="59">
-        <v>1.89E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="Q16" s="59">
         <f t="shared" si="2"/>
-        <v>0.94500000000000006</v>
+        <v>0.6</v>
       </c>
       <c r="R16" s="48"/>
       <c r="S16" s="46"/>
@@ -2039,7 +2043,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="80" t="s">
+      <c r="C17" s="70" t="s">
         <v>76</v>
       </c>
       <c r="D17" s="49" t="s">
@@ -2061,7 +2065,7 @@
         <v>50</v>
       </c>
       <c r="J17" s="49" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K17" s="50" t="s">
         <v>61</v>
@@ -2095,7 +2099,7 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="79" t="s">
+      <c r="C18" s="69" t="s">
         <v>77</v>
       </c>
       <c r="D18" s="46" t="s">
@@ -2117,7 +2121,7 @@
         <v>55</v>
       </c>
       <c r="J18" s="46" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K18" s="47" t="s">
         <v>80</v>
@@ -2151,7 +2155,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="80" t="s">
+      <c r="C19" s="70" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="49" t="s">
@@ -2173,7 +2177,7 @@
         <v>56</v>
       </c>
       <c r="J19" s="49" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K19" s="50" t="s">
         <v>80</v>
@@ -2207,7 +2211,7 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="79" t="s">
+      <c r="C20" s="69" t="s">
         <v>78</v>
       </c>
       <c r="D20" s="46" t="s">
@@ -2229,7 +2233,7 @@
         <v>57</v>
       </c>
       <c r="J20" s="46" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K20" s="47" t="s">
         <v>80</v>
@@ -2271,17 +2275,17 @@
       <c r="K21" s="37"/>
       <c r="L21" s="37"/>
       <c r="M21" s="37"/>
-      <c r="N21" s="77" t="s">
-        <v>95</v>
-      </c>
-      <c r="O21" s="78"/>
-      <c r="P21" s="78"/>
+      <c r="N21" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="O21" s="80"/>
+      <c r="P21" s="80"/>
       <c r="Q21" s="67">
         <f>SUM(Q10:Q20)</f>
-        <v>16.730399999999999</v>
-      </c>
-      <c r="R21" s="73"/>
-      <c r="S21" s="74"/>
+        <v>16.385399999999997</v>
+      </c>
+      <c r="R21" s="75"/>
+      <c r="S21" s="76"/>
     </row>
     <row r="22" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
@@ -2297,17 +2301,17 @@
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
       <c r="M22" s="10"/>
-      <c r="N22" s="77" t="s">
-        <v>96</v>
-      </c>
-      <c r="O22" s="78"/>
-      <c r="P22" s="78"/>
+      <c r="N22" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="O22" s="80"/>
+      <c r="P22" s="80"/>
       <c r="Q22" s="68">
         <f>Q21/5</f>
-        <v>3.3460799999999997</v>
-      </c>
-      <c r="R22" s="75"/>
-      <c r="S22" s="76"/>
+        <v>3.2770799999999993</v>
+      </c>
+      <c r="R22" s="77"/>
+      <c r="S22" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2324,11 +2328,11 @@
     <hyperlink ref="O13" r:id="rId4" xr:uid="{4D21958E-FFB1-43C1-B536-08A12923A302}"/>
     <hyperlink ref="O14" r:id="rId5" xr:uid="{F5C5D409-72B6-4546-9CBC-54F64848BBEA}"/>
     <hyperlink ref="O15" r:id="rId6" xr:uid="{3C85C19D-6630-420B-9B9F-252B3AD39A5C}"/>
-    <hyperlink ref="O16" r:id="rId7" xr:uid="{BEA5D900-E700-4B3D-BCEE-CFED10FF5E4E}"/>
-    <hyperlink ref="O17" r:id="rId8" xr:uid="{43FF55F8-7B69-4F51-A753-0C2F1852F8FC}"/>
-    <hyperlink ref="O18" r:id="rId9" xr:uid="{149427FE-4837-4C89-82FC-B3262B718FBA}"/>
-    <hyperlink ref="O19" r:id="rId10" xr:uid="{F0C766FB-E9F8-4AC6-97DF-8CEDF3D649EC}"/>
-    <hyperlink ref="O20" r:id="rId11" xr:uid="{B20A26D6-3091-4797-B290-C5FE7261CE34}"/>
+    <hyperlink ref="O17" r:id="rId7" xr:uid="{43FF55F8-7B69-4F51-A753-0C2F1852F8FC}"/>
+    <hyperlink ref="O18" r:id="rId8" xr:uid="{149427FE-4837-4C89-82FC-B3262B718FBA}"/>
+    <hyperlink ref="O19" r:id="rId9" xr:uid="{F0C766FB-E9F8-4AC6-97DF-8CEDF3D649EC}"/>
+    <hyperlink ref="O20" r:id="rId10" xr:uid="{B20A26D6-3091-4797-B290-C5FE7261CE34}"/>
+    <hyperlink ref="O16" r:id="rId11" xr:uid="{361F3121-5AA2-4220-A37E-D4519C47E9D6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>

--- a/BOM/Fob_Transmitter/eSpark_BOM_Fob_Transmitter.xlsx
+++ b/BOM/Fob_Transmitter/eSpark_BOM_Fob_Transmitter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25629"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\OliverStanton-WaterMonitor\BOM\Fob_Transmitter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3325A2C2-1FCA-4EB1-8471-942346E1F328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47273CD7-A249-4934-8B2E-EB7A06CD3946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5280" yWindow="3345" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1004,6 +1004,9 @@
     <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1035,9 +1038,6 @@
     <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1415,15 +1415,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
-      <c r="R1" s="71"/>
-      <c r="S1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="73"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1473,7 +1473,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="73"/>
+      <c r="S3" s="74"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1498,7 +1498,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="74"/>
+      <c r="S4" s="75"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1523,7 +1523,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="74"/>
+      <c r="S5" s="75"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1544,7 +1544,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="74"/>
+      <c r="S6" s="75"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1565,7 +1565,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="74"/>
+      <c r="S7" s="75"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1586,7 +1586,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="74"/>
+      <c r="S8" s="75"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1692,11 +1692,11 @@
         <v>82</v>
       </c>
       <c r="P10" s="59">
-        <v>3.49E-2</v>
+        <v>3.1399999999999997E-2</v>
       </c>
       <c r="Q10" s="59">
         <f>P10*N10</f>
-        <v>0.69799999999999995</v>
+        <v>0.62799999999999989</v>
       </c>
       <c r="R10" s="48"/>
       <c r="S10" s="46"/>
@@ -1748,11 +1748,11 @@
         <v>82</v>
       </c>
       <c r="P11" s="60">
-        <v>3.3999999999999998E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="Q11" s="60">
         <f t="shared" ref="Q11:Q20" si="2">P11*N11</f>
-        <v>0.33999999999999997</v>
+        <v>0.27</v>
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="49"/>
@@ -1804,11 +1804,11 @@
         <v>82</v>
       </c>
       <c r="P12" s="59">
-        <v>5.8999999999999999E-3</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="Q12" s="59">
         <f t="shared" si="2"/>
-        <v>0.29499999999999998</v>
+        <v>0.27499999999999997</v>
       </c>
       <c r="R12" s="48"/>
       <c r="S12" s="46"/>
@@ -1860,11 +1860,11 @@
         <v>82</v>
       </c>
       <c r="P13" s="60">
-        <v>5.67E-2</v>
+        <v>4.8099999999999997E-2</v>
       </c>
       <c r="Q13" s="60">
         <f t="shared" si="2"/>
-        <v>0.56699999999999995</v>
+        <v>0.48099999999999998</v>
       </c>
       <c r="R13" s="51"/>
       <c r="S13" s="49"/>
@@ -1916,11 +1916,11 @@
         <v>82</v>
       </c>
       <c r="P14" s="59">
-        <v>2.7400000000000001E-2</v>
+        <v>2.4500000000000001E-2</v>
       </c>
       <c r="Q14" s="59">
         <f t="shared" si="2"/>
-        <v>0.54800000000000004</v>
+        <v>0.49</v>
       </c>
       <c r="R14" s="48"/>
       <c r="S14" s="46"/>
@@ -1972,11 +1972,11 @@
         <v>82</v>
       </c>
       <c r="P15" s="60">
-        <v>1.47E-2</v>
+        <v>1.3299999999999999E-2</v>
       </c>
       <c r="Q15" s="60">
         <f t="shared" si="2"/>
-        <v>0.73499999999999999</v>
+        <v>0.66499999999999992</v>
       </c>
       <c r="R15" s="51"/>
       <c r="S15" s="49"/>
@@ -2002,7 +2002,7 @@
       <c r="G16" s="62">
         <v>61300211121</v>
       </c>
-      <c r="H16" s="81" t="s">
+      <c r="H16" s="71" t="s">
         <v>98</v>
       </c>
       <c r="I16" s="46" t="s">
@@ -2028,11 +2028,11 @@
         <v>82</v>
       </c>
       <c r="P16" s="59">
-        <v>1.2E-2</v>
+        <v>1.35E-2</v>
       </c>
       <c r="Q16" s="59">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="R16" s="48"/>
       <c r="S16" s="46"/>
@@ -2084,11 +2084,11 @@
         <v>82</v>
       </c>
       <c r="P17" s="66">
-        <v>1.5E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q17" s="60">
         <f t="shared" si="2"/>
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="R17" s="51"/>
       <c r="S17" s="49"/>
@@ -2140,11 +2140,11 @@
         <v>82</v>
       </c>
       <c r="P18" s="59">
-        <v>6.4500000000000002E-2</v>
+        <v>5.8799999999999998E-2</v>
       </c>
       <c r="Q18" s="59">
         <f t="shared" si="2"/>
-        <v>1.9350000000000001</v>
+        <v>1.764</v>
       </c>
       <c r="R18" s="48"/>
       <c r="S18" s="46"/>
@@ -2196,11 +2196,11 @@
         <v>82</v>
       </c>
       <c r="P19" s="60">
-        <v>0.7863</v>
+        <v>0.70479999999999998</v>
       </c>
       <c r="Q19" s="60">
         <f t="shared" si="2"/>
-        <v>4.7178000000000004</v>
+        <v>4.2287999999999997</v>
       </c>
       <c r="R19" s="51"/>
       <c r="S19" s="49"/>
@@ -2252,11 +2252,11 @@
         <v>82</v>
       </c>
       <c r="P20" s="59">
-        <v>0.96660000000000001</v>
+        <v>0.88460000000000005</v>
       </c>
       <c r="Q20" s="59">
         <f t="shared" si="2"/>
-        <v>5.7995999999999999</v>
+        <v>5.3076000000000008</v>
       </c>
       <c r="R20" s="48"/>
       <c r="S20" s="46"/>
@@ -2275,17 +2275,17 @@
       <c r="K21" s="37"/>
       <c r="L21" s="37"/>
       <c r="M21" s="37"/>
-      <c r="N21" s="79" t="s">
+      <c r="N21" s="80" t="s">
         <v>93</v>
       </c>
-      <c r="O21" s="80"/>
-      <c r="P21" s="80"/>
+      <c r="O21" s="81"/>
+      <c r="P21" s="81"/>
       <c r="Q21" s="67">
         <f>SUM(Q10:Q20)</f>
-        <v>16.385399999999997</v>
-      </c>
-      <c r="R21" s="75"/>
-      <c r="S21" s="76"/>
+        <v>14.914400000000001</v>
+      </c>
+      <c r="R21" s="76"/>
+      <c r="S21" s="77"/>
     </row>
     <row r="22" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
@@ -2301,17 +2301,17 @@
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
       <c r="M22" s="10"/>
-      <c r="N22" s="79" t="s">
+      <c r="N22" s="80" t="s">
         <v>94</v>
       </c>
-      <c r="O22" s="80"/>
-      <c r="P22" s="80"/>
+      <c r="O22" s="81"/>
+      <c r="P22" s="81"/>
       <c r="Q22" s="68">
         <f>Q21/5</f>
-        <v>3.2770799999999993</v>
-      </c>
-      <c r="R22" s="77"/>
-      <c r="S22" s="78"/>
+        <v>2.9828800000000002</v>
+      </c>
+      <c r="R22" s="78"/>
+      <c r="S22" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/BOM/Fob_Transmitter/eSpark_BOM_Fob_Transmitter.xlsx
+++ b/BOM/Fob_Transmitter/eSpark_BOM_Fob_Transmitter.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25629"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\OliverStanton-WaterMonitor\BOM\Fob_Transmitter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\OliverStanton-WaterMonitor\BOM\Fob_Transmitter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47273CD7-A249-4934-8B2E-EB7A06CD3946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="11790" windowHeight="15360"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="101">
   <si>
     <t>Component list</t>
   </si>
@@ -285,9 +284,6 @@
   </si>
   <si>
     <t>C14664</t>
-  </si>
-  <si>
-    <t>C2935993</t>
   </si>
   <si>
     <t>C492404</t>
@@ -331,18 +327,24 @@
   </si>
   <si>
     <t>C492401</t>
+  </si>
+  <si>
+    <t>C2718488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J1 Female 4 pin Vertical Header Se replace kr dia ha for testing Purpose </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -503,6 +505,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -810,7 +820,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -980,9 +990,6 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1038,6 +1045,12 @@
     <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1379,7 +1392,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:S22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1415,15 +1428,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="73"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="72"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1434,7 +1447,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="52" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
@@ -1459,7 +1472,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
@@ -1473,7 +1486,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="74"/>
+      <c r="S3" s="73"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1484,7 +1497,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="54" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
@@ -1498,7 +1511,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="75"/>
+      <c r="S4" s="74"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1523,7 +1536,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="75"/>
+      <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1544,7 +1557,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="75"/>
+      <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1565,7 +1578,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="75"/>
+      <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1586,7 +1599,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="75"/>
+      <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1618,7 +1631,7 @@
         <v>65</v>
       </c>
       <c r="K9" s="56" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L9" s="30" t="s">
         <v>62</v>
@@ -1651,7 +1664,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="69" t="s">
+      <c r="C10" s="68" t="s">
         <v>73</v>
       </c>
       <c r="D10" s="46" t="s">
@@ -1707,7 +1720,7 @@
         <f t="shared" ref="B11:B19" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="70" t="s">
+      <c r="C11" s="69" t="s">
         <v>73</v>
       </c>
       <c r="D11" s="49" t="s">
@@ -1763,7 +1776,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="69" t="s">
+      <c r="C12" s="68" t="s">
         <v>73</v>
       </c>
       <c r="D12" s="46" t="s">
@@ -1813,13 +1826,13 @@
       <c r="R12" s="48"/>
       <c r="S12" s="46"/>
     </row>
-    <row r="13" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="38">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="70" t="s">
+      <c r="C13" s="69" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="49" t="s">
@@ -1831,17 +1844,17 @@
       <c r="F13" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="G13" s="63" t="s">
+      <c r="G13" s="81" t="s">
         <v>31</v>
       </c>
       <c r="H13" s="49" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="I13" s="49" t="s">
         <v>51</v>
       </c>
       <c r="J13" s="49" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="K13" s="50" t="s">
         <v>80</v>
@@ -1860,13 +1873,15 @@
         <v>82</v>
       </c>
       <c r="P13" s="60">
-        <v>4.8099999999999997E-2</v>
+        <v>4.3200000000000002E-2</v>
       </c>
       <c r="Q13" s="60">
         <f t="shared" si="2"/>
-        <v>0.48099999999999998</v>
-      </c>
-      <c r="R13" s="51"/>
+        <v>0.43200000000000005</v>
+      </c>
+      <c r="R13" s="82" t="s">
+        <v>100</v>
+      </c>
       <c r="S13" s="49"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1875,14 +1890,14 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="69" t="s">
+      <c r="C14" s="68" t="s">
         <v>74</v>
       </c>
       <c r="D14" s="46" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F14" s="46" t="s">
         <v>32</v>
@@ -1897,7 +1912,7 @@
         <v>52</v>
       </c>
       <c r="J14" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K14" s="47" t="s">
         <v>80</v>
@@ -1931,7 +1946,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="70" t="s">
+      <c r="C15" s="69" t="s">
         <v>75</v>
       </c>
       <c r="D15" s="49" t="s">
@@ -1953,7 +1968,7 @@
         <v>53</v>
       </c>
       <c r="J15" s="49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K15" s="50" t="s">
         <v>80</v>
@@ -1987,7 +2002,7 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="69" t="s">
+      <c r="C16" s="68" t="s">
         <v>74</v>
       </c>
       <c r="D16" s="46" t="s">
@@ -2002,14 +2017,14 @@
       <c r="G16" s="62">
         <v>61300211121</v>
       </c>
-      <c r="H16" s="71" t="s">
-        <v>98</v>
+      <c r="H16" s="70" t="s">
+        <v>97</v>
       </c>
       <c r="I16" s="46" t="s">
         <v>54</v>
       </c>
       <c r="J16" s="46" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K16" s="47" t="s">
         <v>80</v>
@@ -2043,7 +2058,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="70" t="s">
+      <c r="C17" s="69" t="s">
         <v>76</v>
       </c>
       <c r="D17" s="49" t="s">
@@ -2065,7 +2080,7 @@
         <v>50</v>
       </c>
       <c r="J17" s="49" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K17" s="50" t="s">
         <v>61</v>
@@ -2080,10 +2095,10 @@
       <c r="N17" s="49">
         <v>100</v>
       </c>
-      <c r="O17" s="65" t="s">
+      <c r="O17" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="P17" s="66">
+      <c r="P17" s="65">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q17" s="60">
@@ -2099,7 +2114,7 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="69" t="s">
+      <c r="C18" s="68" t="s">
         <v>77</v>
       </c>
       <c r="D18" s="46" t="s">
@@ -2111,7 +2126,7 @@
       <c r="F18" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="G18" s="64" t="s">
+      <c r="G18" s="63" t="s">
         <v>36</v>
       </c>
       <c r="H18" s="46" t="s">
@@ -2121,7 +2136,7 @@
         <v>55</v>
       </c>
       <c r="J18" s="46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K18" s="47" t="s">
         <v>80</v>
@@ -2155,7 +2170,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="70" t="s">
+      <c r="C19" s="69" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="49" t="s">
@@ -2177,7 +2192,7 @@
         <v>56</v>
       </c>
       <c r="J19" s="49" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K19" s="50" t="s">
         <v>80</v>
@@ -2211,7 +2226,7 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="69" t="s">
+      <c r="C20" s="68" t="s">
         <v>78</v>
       </c>
       <c r="D20" s="46" t="s">
@@ -2233,7 +2248,7 @@
         <v>57</v>
       </c>
       <c r="J20" s="46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K20" s="47" t="s">
         <v>80</v>
@@ -2275,17 +2290,17 @@
       <c r="K21" s="37"/>
       <c r="L21" s="37"/>
       <c r="M21" s="37"/>
-      <c r="N21" s="80" t="s">
-        <v>93</v>
-      </c>
-      <c r="O21" s="81"/>
-      <c r="P21" s="81"/>
-      <c r="Q21" s="67">
+      <c r="N21" s="79" t="s">
+        <v>92</v>
+      </c>
+      <c r="O21" s="80"/>
+      <c r="P21" s="80"/>
+      <c r="Q21" s="66">
         <f>SUM(Q10:Q20)</f>
-        <v>14.914400000000001</v>
-      </c>
-      <c r="R21" s="76"/>
-      <c r="S21" s="77"/>
+        <v>14.865400000000001</v>
+      </c>
+      <c r="R21" s="75"/>
+      <c r="S21" s="76"/>
     </row>
     <row r="22" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
@@ -2301,17 +2316,17 @@
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
       <c r="M22" s="10"/>
-      <c r="N22" s="80" t="s">
-        <v>94</v>
-      </c>
-      <c r="O22" s="81"/>
-      <c r="P22" s="81"/>
-      <c r="Q22" s="68">
+      <c r="N22" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="O22" s="80"/>
+      <c r="P22" s="80"/>
+      <c r="Q22" s="67">
         <f>Q21/5</f>
-        <v>2.9828800000000002</v>
-      </c>
-      <c r="R22" s="78"/>
-      <c r="S22" s="79"/>
+        <v>2.9730800000000004</v>
+      </c>
+      <c r="R22" s="77"/>
+      <c r="S22" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2322,17 +2337,17 @@
     <mergeCell ref="N22:P22"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1" xr:uid="{9B08C246-1443-476F-8400-7BF3E1401704}"/>
-    <hyperlink ref="O11" r:id="rId2" xr:uid="{B8781B98-3701-4BDE-BA8A-0948A879AEBE}"/>
-    <hyperlink ref="O12" r:id="rId3" xr:uid="{6083E340-8613-4175-983D-DF68D511270B}"/>
-    <hyperlink ref="O13" r:id="rId4" xr:uid="{4D21958E-FFB1-43C1-B536-08A12923A302}"/>
-    <hyperlink ref="O14" r:id="rId5" xr:uid="{F5C5D409-72B6-4546-9CBC-54F64848BBEA}"/>
-    <hyperlink ref="O15" r:id="rId6" xr:uid="{3C85C19D-6630-420B-9B9F-252B3AD39A5C}"/>
-    <hyperlink ref="O17" r:id="rId7" xr:uid="{43FF55F8-7B69-4F51-A753-0C2F1852F8FC}"/>
-    <hyperlink ref="O18" r:id="rId8" xr:uid="{149427FE-4837-4C89-82FC-B3262B718FBA}"/>
-    <hyperlink ref="O19" r:id="rId9" xr:uid="{F0C766FB-E9F8-4AC6-97DF-8CEDF3D649EC}"/>
-    <hyperlink ref="O20" r:id="rId10" xr:uid="{B20A26D6-3091-4797-B290-C5FE7261CE34}"/>
-    <hyperlink ref="O16" r:id="rId11" xr:uid="{361F3121-5AA2-4220-A37E-D4519C47E9D6}"/>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O12" r:id="rId3"/>
+    <hyperlink ref="O14" r:id="rId4"/>
+    <hyperlink ref="O15" r:id="rId5"/>
+    <hyperlink ref="O17" r:id="rId6"/>
+    <hyperlink ref="O18" r:id="rId7"/>
+    <hyperlink ref="O19" r:id="rId8"/>
+    <hyperlink ref="O20" r:id="rId9"/>
+    <hyperlink ref="O16" r:id="rId10"/>
+    <hyperlink ref="O13" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>

--- a/BOM/Fob_Transmitter/eSpark_BOM_Fob_Transmitter.xlsx
+++ b/BOM/Fob_Transmitter/eSpark_BOM_Fob_Transmitter.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="105">
   <si>
     <t>Component list</t>
   </si>
@@ -333,6 +333,18 @@
   </si>
   <si>
     <t xml:space="preserve">J1 Female 4 pin Vertical Header Se replace kr dia ha for testing Purpose </t>
+  </si>
+  <si>
+    <t>Transmitter Module</t>
+  </si>
+  <si>
+    <t>C381208</t>
+  </si>
+  <si>
+    <t>DL-TX1A-433M</t>
+  </si>
+  <si>
+    <t>DreamLNK</t>
   </si>
 </sst>
 </file>
@@ -514,7 +526,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -530,12 +542,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF03A4CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -820,7 +826,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -888,13 +894,13 @@
     <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -913,7 +919,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -948,15 +954,6 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -969,7 +966,7 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -981,24 +978,12 @@
     <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1006,9 +991,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1046,10 +1028,31 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1394,7 +1397,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -1428,15 +1431,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
-      <c r="R1" s="71"/>
-      <c r="S1" s="72"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="64"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1446,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="11"/>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="49" t="s">
         <v>95</v>
       </c>
       <c r="G2" s="12"/>
@@ -1471,7 +1474,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="13"/>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="50" t="s">
         <v>96</v>
       </c>
       <c r="G3" s="13"/>
@@ -1486,7 +1489,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="73"/>
+      <c r="S3" s="65"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1496,7 +1499,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="13"/>
-      <c r="F4" s="54" t="s">
+      <c r="F4" s="51" t="s">
         <v>96</v>
       </c>
       <c r="G4" s="14"/>
@@ -1511,7 +1514,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="74"/>
+      <c r="S4" s="66"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1521,7 +1524,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="55" t="s">
+      <c r="F5" s="52" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="15"/>
@@ -1536,7 +1539,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="74"/>
+      <c r="S5" s="66"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1557,7 +1560,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="74"/>
+      <c r="S6" s="66"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1578,7 +1581,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="74"/>
+      <c r="S7" s="66"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1599,7 +1602,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="74"/>
+      <c r="S8" s="66"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1630,7 +1633,7 @@
       <c r="J9" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="K9" s="56" t="s">
+      <c r="K9" s="53" t="s">
         <v>94</v>
       </c>
       <c r="L9" s="30" t="s">
@@ -1664,7 +1667,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="68" t="s">
+      <c r="C10" s="61" t="s">
         <v>73</v>
       </c>
       <c r="D10" s="46" t="s">
@@ -1701,13 +1704,13 @@
       <c r="N10" s="46">
         <v>20</v>
       </c>
-      <c r="O10" s="58" t="s">
+      <c r="O10" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="P10" s="59">
+      <c r="P10" s="56">
         <v>3.1399999999999997E-2</v>
       </c>
-      <c r="Q10" s="59">
+      <c r="Q10" s="56">
         <f>P10*N10</f>
         <v>0.62799999999999989</v>
       </c>
@@ -1720,55 +1723,55 @@
         <f t="shared" ref="B11:B19" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="69" t="s">
+      <c r="C11" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="49" t="s">
+      <c r="D11" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="50" t="s">
+      <c r="E11" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="49" t="s">
+      <c r="F11" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="50" t="s">
+      <c r="G11" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="49" t="s">
+      <c r="H11" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="I11" s="49" t="s">
+      <c r="I11" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="J11" s="49" t="s">
+      <c r="J11" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="50" t="s">
+      <c r="K11" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="49">
+      <c r="L11" s="75">
         <v>7</v>
       </c>
-      <c r="M11" s="49">
-        <f t="shared" ref="M11:M20" si="1">L11*5</f>
+      <c r="M11" s="75">
+        <f t="shared" ref="M11:M21" si="1">L11*5</f>
         <v>35</v>
       </c>
-      <c r="N11" s="49">
+      <c r="N11" s="75">
         <v>100</v>
       </c>
-      <c r="O11" s="61" t="s">
+      <c r="O11" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="P11" s="60">
+      <c r="P11" s="78">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="Q11" s="60">
+      <c r="Q11" s="78">
         <f t="shared" ref="Q11:Q20" si="2">P11*N11</f>
         <v>0.27</v>
       </c>
-      <c r="R11" s="51"/>
-      <c r="S11" s="49"/>
+      <c r="R11" s="79"/>
+      <c r="S11" s="75"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
@@ -1776,7 +1779,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="61" t="s">
         <v>73</v>
       </c>
       <c r="D12" s="46" t="s">
@@ -1813,13 +1816,13 @@
       <c r="N12" s="46">
         <v>50</v>
       </c>
-      <c r="O12" s="58" t="s">
+      <c r="O12" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="P12" s="59">
+      <c r="P12" s="56">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="Q12" s="59">
+      <c r="Q12" s="56">
         <f t="shared" si="2"/>
         <v>0.27499999999999997</v>
       </c>
@@ -1832,57 +1835,57 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="49" t="s">
+      <c r="D13" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="50" t="s">
+      <c r="E13" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="49" t="s">
+      <c r="F13" s="75" t="s">
         <v>79</v>
       </c>
-      <c r="G13" s="81" t="s">
+      <c r="G13" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="49" t="s">
+      <c r="H13" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="I13" s="49" t="s">
+      <c r="I13" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="J13" s="49" t="s">
+      <c r="J13" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="K13" s="50" t="s">
+      <c r="K13" s="76" t="s">
         <v>80</v>
       </c>
-      <c r="L13" s="49">
+      <c r="L13" s="75">
         <v>1</v>
       </c>
-      <c r="M13" s="49">
+      <c r="M13" s="75">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N13" s="49">
+      <c r="N13" s="75">
         <v>10</v>
       </c>
-      <c r="O13" s="61" t="s">
+      <c r="O13" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="P13" s="60">
+      <c r="P13" s="78">
         <v>4.3200000000000002E-2</v>
       </c>
-      <c r="Q13" s="60">
+      <c r="Q13" s="78">
         <f t="shared" si="2"/>
         <v>0.43200000000000005</v>
       </c>
-      <c r="R13" s="82" t="s">
+      <c r="R13" s="81" t="s">
         <v>100</v>
       </c>
-      <c r="S13" s="49"/>
+      <c r="S13" s="75"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
@@ -1890,7 +1893,7 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="61" t="s">
         <v>74</v>
       </c>
       <c r="D14" s="46" t="s">
@@ -1927,13 +1930,13 @@
       <c r="N14" s="46">
         <v>20</v>
       </c>
-      <c r="O14" s="58" t="s">
+      <c r="O14" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="P14" s="59">
+      <c r="P14" s="56">
         <v>2.4500000000000001E-2</v>
       </c>
-      <c r="Q14" s="59">
+      <c r="Q14" s="56">
         <f t="shared" si="2"/>
         <v>0.49</v>
       </c>
@@ -1946,55 +1949,55 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="69" t="s">
+      <c r="C15" s="74" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="49" t="s">
+      <c r="D15" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="50" t="s">
+      <c r="E15" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="49" t="s">
+      <c r="F15" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="50" t="s">
+      <c r="G15" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="49" t="s">
+      <c r="H15" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="I15" s="49" t="s">
+      <c r="I15" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="J15" s="49" t="s">
+      <c r="J15" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K15" s="50" t="s">
+      <c r="K15" s="76" t="s">
         <v>80</v>
       </c>
-      <c r="L15" s="49">
+      <c r="L15" s="75">
         <v>1</v>
       </c>
-      <c r="M15" s="49">
+      <c r="M15" s="75">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N15" s="49">
+      <c r="N15" s="75">
         <v>50</v>
       </c>
-      <c r="O15" s="61" t="s">
+      <c r="O15" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="P15" s="60">
+      <c r="P15" s="78">
         <v>1.3299999999999999E-2</v>
       </c>
-      <c r="Q15" s="60">
+      <c r="Q15" s="78">
         <f t="shared" si="2"/>
         <v>0.66499999999999992</v>
       </c>
-      <c r="R15" s="51"/>
-      <c r="S15" s="49"/>
+      <c r="R15" s="79"/>
+      <c r="S15" s="75"/>
     </row>
     <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
@@ -2002,7 +2005,7 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="61" t="s">
         <v>74</v>
       </c>
       <c r="D16" s="46" t="s">
@@ -2014,10 +2017,10 @@
       <c r="F16" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="G16" s="62">
+      <c r="G16" s="57">
         <v>61300211121</v>
       </c>
-      <c r="H16" s="70" t="s">
+      <c r="H16" s="62" t="s">
         <v>97</v>
       </c>
       <c r="I16" s="46" t="s">
@@ -2039,13 +2042,13 @@
       <c r="N16" s="46">
         <v>50</v>
       </c>
-      <c r="O16" s="58" t="s">
+      <c r="O16" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="P16" s="59">
+      <c r="P16" s="56">
         <v>1.35E-2</v>
       </c>
-      <c r="Q16" s="59">
+      <c r="Q16" s="56">
         <f t="shared" si="2"/>
         <v>0.67500000000000004</v>
       </c>
@@ -2058,55 +2061,55 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="69" t="s">
+      <c r="C17" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="49" t="s">
+      <c r="D17" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="50" t="s">
+      <c r="E17" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="49" t="s">
+      <c r="F17" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="G17" s="50" t="s">
+      <c r="G17" s="76" t="s">
         <v>45</v>
       </c>
-      <c r="H17" s="49" t="s">
+      <c r="H17" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="I17" s="49" t="s">
+      <c r="I17" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="J17" s="49" t="s">
+      <c r="J17" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="K17" s="50" t="s">
+      <c r="K17" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="L17" s="49">
+      <c r="L17" s="75">
         <v>5</v>
       </c>
-      <c r="M17" s="49">
+      <c r="M17" s="75">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="N17" s="49">
+      <c r="N17" s="75">
         <v>100</v>
       </c>
-      <c r="O17" s="64" t="s">
+      <c r="O17" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="P17" s="65">
+      <c r="P17" s="56">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q17" s="60">
+      <c r="Q17" s="78">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="R17" s="51"/>
-      <c r="S17" s="49"/>
+      <c r="R17" s="79"/>
+      <c r="S17" s="75"/>
     </row>
     <row r="18" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
@@ -2114,7 +2117,7 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="61" t="s">
         <v>77</v>
       </c>
       <c r="D18" s="46" t="s">
@@ -2126,7 +2129,7 @@
       <c r="F18" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="G18" s="63" t="s">
+      <c r="G18" s="58" t="s">
         <v>36</v>
       </c>
       <c r="H18" s="46" t="s">
@@ -2151,13 +2154,13 @@
       <c r="N18" s="46">
         <v>30</v>
       </c>
-      <c r="O18" s="58" t="s">
+      <c r="O18" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="P18" s="59">
+      <c r="P18" s="56">
         <v>5.8799999999999998E-2</v>
       </c>
-      <c r="Q18" s="59">
+      <c r="Q18" s="56">
         <f t="shared" si="2"/>
         <v>1.764</v>
       </c>
@@ -2170,55 +2173,55 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="69" t="s">
+      <c r="C19" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="49" t="s">
+      <c r="D19" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="50" t="s">
+      <c r="E19" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="49" t="s">
+      <c r="F19" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="G19" s="50" t="s">
+      <c r="G19" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="H19" s="49" t="s">
+      <c r="H19" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="I19" s="49" t="s">
+      <c r="I19" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="J19" s="49" t="s">
+      <c r="J19" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="K19" s="50" t="s">
+      <c r="K19" s="76" t="s">
         <v>80</v>
       </c>
-      <c r="L19" s="49">
+      <c r="L19" s="75">
         <v>1</v>
       </c>
-      <c r="M19" s="49">
+      <c r="M19" s="75">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N19" s="49">
+      <c r="N19" s="75">
         <v>6</v>
       </c>
-      <c r="O19" s="61" t="s">
+      <c r="O19" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="P19" s="60">
+      <c r="P19" s="78">
         <v>0.70479999999999998</v>
       </c>
-      <c r="Q19" s="60">
+      <c r="Q19" s="78">
         <f t="shared" si="2"/>
         <v>4.2287999999999997</v>
       </c>
-      <c r="R19" s="51"/>
-      <c r="S19" s="49"/>
+      <c r="R19" s="79"/>
+      <c r="S19" s="75"/>
     </row>
     <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
@@ -2226,7 +2229,7 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="61" t="s">
         <v>78</v>
       </c>
       <c r="D20" s="46" t="s">
@@ -2241,7 +2244,7 @@
       <c r="G20" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="H20" s="57" t="s">
+      <c r="H20" s="54" t="s">
         <v>80</v>
       </c>
       <c r="I20" s="46" t="s">
@@ -2253,7 +2256,7 @@
       <c r="K20" s="47" t="s">
         <v>80</v>
       </c>
-      <c r="L20" s="57">
+      <c r="L20" s="54">
         <v>1</v>
       </c>
       <c r="M20" s="46">
@@ -2263,78 +2266,132 @@
       <c r="N20" s="46">
         <v>6</v>
       </c>
-      <c r="O20" s="58" t="s">
+      <c r="O20" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="P20" s="59">
+      <c r="P20" s="56">
         <v>0.88460000000000005</v>
       </c>
-      <c r="Q20" s="59">
+      <c r="Q20" s="56">
         <f t="shared" si="2"/>
         <v>5.3076000000000008</v>
       </c>
       <c r="R20" s="48"/>
       <c r="S20" s="46"/>
     </row>
-    <row r="21" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="37"/>
-      <c r="L21" s="37"/>
-      <c r="M21" s="37"/>
-      <c r="N21" s="79" t="s">
-        <v>92</v>
-      </c>
-      <c r="O21" s="80"/>
-      <c r="P21" s="80"/>
-      <c r="Q21" s="66">
-        <f>SUM(Q10:Q20)</f>
-        <v>14.865400000000001</v>
-      </c>
-      <c r="R21" s="75"/>
-      <c r="S21" s="76"/>
+      <c r="B21" s="38">
+        <f t="shared" ref="B21" si="3">ROW(B21) - ROW($B$9)</f>
+        <v>12</v>
+      </c>
+      <c r="C21" s="61" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="H21" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="J21" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="K21" s="47"/>
+      <c r="L21" s="54">
+        <v>1</v>
+      </c>
+      <c r="M21" s="46">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="N21" s="46">
+        <v>5</v>
+      </c>
+      <c r="O21" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="P21" s="56">
+        <v>1.0251999999999999</v>
+      </c>
+      <c r="Q21" s="73">
+        <f>P21*N21</f>
+        <v>5.1259999999999994</v>
+      </c>
+      <c r="R21" s="48"/>
+      <c r="S21" s="46"/>
     </row>
     <row r="22" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="79" t="s">
+      <c r="B22" s="33"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="37"/>
+      <c r="M22" s="37"/>
+      <c r="N22" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="O22" s="72"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="59">
+        <f>SUM(Q10:Q21)</f>
+        <v>19.991399999999999</v>
+      </c>
+      <c r="R22" s="67"/>
+      <c r="S22" s="68"/>
+    </row>
+    <row r="23" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="71" t="s">
         <v>93</v>
       </c>
-      <c r="O22" s="80"/>
-      <c r="P22" s="80"/>
-      <c r="Q22" s="67">
-        <f>Q21/5</f>
-        <v>2.9730800000000004</v>
-      </c>
-      <c r="R22" s="77"/>
-      <c r="S22" s="78"/>
+      <c r="O23" s="72"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="60">
+        <f>Q22/5</f>
+        <v>3.9982799999999998</v>
+      </c>
+      <c r="R23" s="69"/>
+      <c r="S23" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R21:S22"/>
-    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R22:S23"/>
     <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N23:P23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -2345,12 +2402,13 @@
     <hyperlink ref="O17" r:id="rId6"/>
     <hyperlink ref="O18" r:id="rId7"/>
     <hyperlink ref="O19" r:id="rId8"/>
-    <hyperlink ref="O20" r:id="rId9"/>
-    <hyperlink ref="O16" r:id="rId10"/>
-    <hyperlink ref="O13" r:id="rId11"/>
+    <hyperlink ref="O16" r:id="rId9"/>
+    <hyperlink ref="O13" r:id="rId10"/>
+    <hyperlink ref="O20" r:id="rId11"/>
+    <hyperlink ref="O21" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>
-  <drawing r:id="rId13"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
+  <drawing r:id="rId14"/>
 </worksheet>
 </file>
--- a/BOM/Fob_Transmitter/eSpark_BOM_Fob_Transmitter.xlsx
+++ b/BOM/Fob_Transmitter/eSpark_BOM_Fob_Transmitter.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\OliverStanton-WaterMonitor\BOM\Fob_Transmitter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\OliverStanton-WaterMonitor\BOM\Fob_Transmitter\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -329,12 +329,6 @@
     <t>C492401</t>
   </si>
   <si>
-    <t>C2718488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J1 Female 4 pin Vertical Header Se replace kr dia ha for testing Purpose </t>
-  </si>
-  <si>
     <t>Transmitter Module</t>
   </si>
   <si>
@@ -345,12 +339,18 @@
   </si>
   <si>
     <t>DreamLNK</t>
+  </si>
+  <si>
+    <t>C2897366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J1 Female 3 pin Vertical Header Se replace kr dia ha for testing Purpose </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -996,6 +996,33 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1027,33 +1054,6 @@
     <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1099,7 +1099,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1431,15 +1431,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
-      <c r="R1" s="63"/>
-      <c r="S1" s="64"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="73"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1489,7 +1489,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="65"/>
+      <c r="S3" s="74"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1514,7 +1514,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="66"/>
+      <c r="S4" s="75"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1539,7 +1539,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="66"/>
+      <c r="S5" s="75"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1560,7 +1560,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="66"/>
+      <c r="S6" s="75"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1581,7 +1581,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="66"/>
+      <c r="S7" s="75"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1602,7 +1602,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="66"/>
+      <c r="S8" s="75"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1723,55 +1723,55 @@
         <f t="shared" ref="B11:B19" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="74" t="s">
+      <c r="C11" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="75" t="s">
+      <c r="D11" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="76" t="s">
+      <c r="E11" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="75" t="s">
+      <c r="F11" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="76" t="s">
+      <c r="G11" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="75" t="s">
+      <c r="H11" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="I11" s="75" t="s">
+      <c r="I11" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="J11" s="75" t="s">
+      <c r="J11" s="65" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="76" t="s">
+      <c r="K11" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="75">
+      <c r="L11" s="65">
         <v>7</v>
       </c>
-      <c r="M11" s="75">
+      <c r="M11" s="65">
         <f t="shared" ref="M11:M21" si="1">L11*5</f>
         <v>35</v>
       </c>
-      <c r="N11" s="75">
+      <c r="N11" s="65">
         <v>100</v>
       </c>
-      <c r="O11" s="77" t="s">
+      <c r="O11" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="P11" s="78">
+      <c r="P11" s="68">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="Q11" s="78">
+      <c r="Q11" s="68">
         <f t="shared" ref="Q11:Q20" si="2">P11*N11</f>
         <v>0.27</v>
       </c>
-      <c r="R11" s="79"/>
-      <c r="S11" s="75"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="65"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
@@ -1835,57 +1835,57 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="74" t="s">
+      <c r="C13" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="75" t="s">
+      <c r="D13" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="76" t="s">
+      <c r="E13" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="75" t="s">
+      <c r="F13" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="G13" s="80" t="s">
+      <c r="G13" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="75" t="s">
-        <v>99</v>
-      </c>
-      <c r="I13" s="75" t="s">
+      <c r="H13" s="65" t="s">
+        <v>103</v>
+      </c>
+      <c r="I13" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="J13" s="75" t="s">
-        <v>99</v>
-      </c>
-      <c r="K13" s="76" t="s">
+      <c r="J13" s="65" t="s">
+        <v>103</v>
+      </c>
+      <c r="K13" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="L13" s="75">
+      <c r="L13" s="65">
         <v>1</v>
       </c>
-      <c r="M13" s="75">
+      <c r="M13" s="65">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N13" s="75">
+      <c r="N13" s="65">
         <v>10</v>
       </c>
-      <c r="O13" s="77" t="s">
+      <c r="O13" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="P13" s="78">
-        <v>4.3200000000000002E-2</v>
-      </c>
-      <c r="Q13" s="78">
+      <c r="P13" s="68">
+        <v>5.9799999999999999E-2</v>
+      </c>
+      <c r="Q13" s="68">
         <f t="shared" si="2"/>
-        <v>0.43200000000000005</v>
-      </c>
-      <c r="R13" s="81" t="s">
-        <v>100</v>
-      </c>
-      <c r="S13" s="75"/>
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="R13" s="71" t="s">
+        <v>104</v>
+      </c>
+      <c r="S13" s="65"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
@@ -1949,55 +1949,55 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="74" t="s">
+      <c r="C15" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="75" t="s">
+      <c r="D15" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="76" t="s">
+      <c r="E15" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="75" t="s">
+      <c r="F15" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="76" t="s">
+      <c r="G15" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="75" t="s">
+      <c r="H15" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="I15" s="75" t="s">
+      <c r="I15" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="J15" s="75" t="s">
+      <c r="J15" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="K15" s="76" t="s">
+      <c r="K15" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="L15" s="75">
+      <c r="L15" s="65">
         <v>1</v>
       </c>
-      <c r="M15" s="75">
+      <c r="M15" s="65">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N15" s="75">
+      <c r="N15" s="65">
         <v>50</v>
       </c>
-      <c r="O15" s="77" t="s">
+      <c r="O15" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="P15" s="78">
+      <c r="P15" s="68">
         <v>1.3299999999999999E-2</v>
       </c>
-      <c r="Q15" s="78">
+      <c r="Q15" s="68">
         <f t="shared" si="2"/>
         <v>0.66499999999999992</v>
       </c>
-      <c r="R15" s="79"/>
-      <c r="S15" s="75"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="65"/>
     </row>
     <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
@@ -2061,41 +2061,41 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="74" t="s">
+      <c r="C17" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="75" t="s">
+      <c r="D17" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="76" t="s">
+      <c r="E17" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="75" t="s">
+      <c r="F17" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="G17" s="76" t="s">
+      <c r="G17" s="66" t="s">
         <v>45</v>
       </c>
-      <c r="H17" s="75" t="s">
+      <c r="H17" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="I17" s="75" t="s">
+      <c r="I17" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="J17" s="75" t="s">
+      <c r="J17" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="K17" s="76" t="s">
+      <c r="K17" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="L17" s="75">
+      <c r="L17" s="65">
         <v>5</v>
       </c>
-      <c r="M17" s="75">
+      <c r="M17" s="65">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="N17" s="75">
+      <c r="N17" s="65">
         <v>100</v>
       </c>
       <c r="O17" s="55" t="s">
@@ -2104,12 +2104,12 @@
       <c r="P17" s="56">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q17" s="78">
+      <c r="Q17" s="68">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="R17" s="79"/>
-      <c r="S17" s="75"/>
+      <c r="R17" s="69"/>
+      <c r="S17" s="65"/>
     </row>
     <row r="18" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
@@ -2173,55 +2173,55 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="74" t="s">
+      <c r="C19" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="75" t="s">
+      <c r="D19" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="76" t="s">
+      <c r="E19" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="75" t="s">
+      <c r="F19" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="G19" s="76" t="s">
+      <c r="G19" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="H19" s="75" t="s">
+      <c r="H19" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="I19" s="75" t="s">
+      <c r="I19" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="J19" s="75" t="s">
+      <c r="J19" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="K19" s="76" t="s">
+      <c r="K19" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="L19" s="75">
+      <c r="L19" s="65">
         <v>1</v>
       </c>
-      <c r="M19" s="75">
+      <c r="M19" s="65">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N19" s="75">
+      <c r="N19" s="65">
         <v>6</v>
       </c>
-      <c r="O19" s="77" t="s">
+      <c r="O19" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="P19" s="78">
+      <c r="P19" s="68">
         <v>0.70479999999999998</v>
       </c>
-      <c r="Q19" s="78">
+      <c r="Q19" s="68">
         <f t="shared" si="2"/>
         <v>4.2287999999999997</v>
       </c>
-      <c r="R19" s="79"/>
-      <c r="S19" s="75"/>
+      <c r="R19" s="69"/>
+      <c r="S19" s="65"/>
     </row>
     <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
@@ -2286,7 +2286,7 @@
         <v>12</v>
       </c>
       <c r="C21" s="61" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D21" s="46" t="s">
         <v>80</v>
@@ -2298,16 +2298,16 @@
         <v>79</v>
       </c>
       <c r="G21" s="47" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H21" s="54" t="s">
         <v>80</v>
       </c>
       <c r="I21" s="46" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J21" s="46" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K21" s="47"/>
       <c r="L21" s="54">
@@ -2326,7 +2326,7 @@
       <c r="P21" s="56">
         <v>1.0251999999999999</v>
       </c>
-      <c r="Q21" s="73">
+      <c r="Q21" s="63">
         <f>P21*N21</f>
         <v>5.1259999999999994</v>
       </c>
@@ -2347,17 +2347,17 @@
       <c r="K22" s="37"/>
       <c r="L22" s="37"/>
       <c r="M22" s="37"/>
-      <c r="N22" s="71" t="s">
+      <c r="N22" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="O22" s="72"/>
-      <c r="P22" s="72"/>
+      <c r="O22" s="81"/>
+      <c r="P22" s="81"/>
       <c r="Q22" s="59">
         <f>SUM(Q10:Q21)</f>
-        <v>19.991399999999999</v>
-      </c>
-      <c r="R22" s="67"/>
-      <c r="S22" s="68"/>
+        <v>20.157400000000003</v>
+      </c>
+      <c r="R22" s="76"/>
+      <c r="S22" s="77"/>
     </row>
     <row r="23" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
@@ -2373,17 +2373,17 @@
       <c r="K23" s="10"/>
       <c r="L23" s="10"/>
       <c r="M23" s="10"/>
-      <c r="N23" s="71" t="s">
+      <c r="N23" s="80" t="s">
         <v>93</v>
       </c>
-      <c r="O23" s="72"/>
-      <c r="P23" s="72"/>
+      <c r="O23" s="81"/>
+      <c r="P23" s="81"/>
       <c r="Q23" s="60">
         <f>Q22/5</f>
-        <v>3.9982799999999998</v>
-      </c>
-      <c r="R23" s="69"/>
-      <c r="S23" s="70"/>
+        <v>4.0314800000000002</v>
+      </c>
+      <c r="R23" s="78"/>
+      <c r="S23" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/BOM/Fob_Transmitter/eSpark_BOM_Fob_Transmitter.xlsx
+++ b/BOM/Fob_Transmitter/eSpark_BOM_Fob_Transmitter.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="106">
   <si>
     <t>Component list</t>
   </si>
@@ -329,12 +329,6 @@
     <t>C492401</t>
   </si>
   <si>
-    <t>C2718488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J1 Female 4 pin Vertical Header Se replace kr dia ha for testing Purpose </t>
-  </si>
-  <si>
     <t>Transmitter Module</t>
   </si>
   <si>
@@ -345,6 +339,15 @@
   </si>
   <si>
     <t>DreamLNK</t>
+  </si>
+  <si>
+    <t>MTF185-103SY1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J1 Female 3 pin Vertical Header Se replace kr dia ha for testing Purpose </t>
+  </si>
+  <si>
+    <t>C358717</t>
   </si>
 </sst>
 </file>
@@ -826,7 +829,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -996,6 +999,30 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1028,33 +1055,29 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1403,7 +1426,7 @@
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
     <col min="3" max="3" width="18" style="26" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.85546875" customWidth="1"/>
+    <col min="5" max="5" width="32.7109375" customWidth="1"/>
     <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
@@ -1431,15 +1454,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
-      <c r="R1" s="63"/>
-      <c r="S1" s="64"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="72"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1489,7 +1512,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="65"/>
+      <c r="S3" s="73"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1514,7 +1537,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="66"/>
+      <c r="S4" s="74"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1539,7 +1562,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="66"/>
+      <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1560,7 +1583,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="66"/>
+      <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1581,7 +1604,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="66"/>
+      <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1602,7 +1625,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="66"/>
+      <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1723,55 +1746,55 @@
         <f t="shared" ref="B11:B19" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="74" t="s">
+      <c r="C11" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="75" t="s">
+      <c r="D11" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="76" t="s">
+      <c r="E11" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="75" t="s">
+      <c r="F11" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="76" t="s">
+      <c r="G11" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="75" t="s">
+      <c r="H11" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="I11" s="75" t="s">
+      <c r="I11" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="J11" s="75" t="s">
+      <c r="J11" s="65" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="76" t="s">
+      <c r="K11" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="75">
+      <c r="L11" s="65">
         <v>7</v>
       </c>
-      <c r="M11" s="75">
+      <c r="M11" s="65">
         <f t="shared" ref="M11:M21" si="1">L11*5</f>
         <v>35</v>
       </c>
-      <c r="N11" s="75">
+      <c r="N11" s="65">
         <v>100</v>
       </c>
-      <c r="O11" s="77" t="s">
+      <c r="O11" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="P11" s="78">
+      <c r="P11" s="68">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="Q11" s="78">
+      <c r="Q11" s="68">
         <f t="shared" ref="Q11:Q20" si="2">P11*N11</f>
         <v>0.27</v>
       </c>
-      <c r="R11" s="79"/>
-      <c r="S11" s="75"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="65"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
@@ -1829,63 +1852,63 @@
       <c r="R12" s="48"/>
       <c r="S12" s="46"/>
     </row>
-    <row r="13" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="38">
+    <row r="13" spans="1:19" s="89" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="81"/>
+      <c r="B13" s="82">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="74" t="s">
+      <c r="C13" s="83" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="75" t="s">
+      <c r="D13" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="76" t="s">
+      <c r="E13" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="75" t="s">
+      <c r="F13" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="G13" s="80" t="s">
+      <c r="G13" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="75" t="s">
-        <v>99</v>
-      </c>
-      <c r="I13" s="75" t="s">
+      <c r="H13" s="84" t="s">
+        <v>103</v>
+      </c>
+      <c r="I13" s="84" t="s">
         <v>51</v>
       </c>
-      <c r="J13" s="75" t="s">
-        <v>99</v>
-      </c>
-      <c r="K13" s="76" t="s">
+      <c r="J13" s="84" t="s">
+        <v>105</v>
+      </c>
+      <c r="K13" s="85" t="s">
         <v>80</v>
       </c>
-      <c r="L13" s="75">
+      <c r="L13" s="84">
         <v>1</v>
       </c>
-      <c r="M13" s="75">
+      <c r="M13" s="84">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N13" s="75">
+      <c r="N13" s="84">
         <v>10</v>
       </c>
-      <c r="O13" s="77" t="s">
+      <c r="O13" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="P13" s="78">
-        <v>4.3200000000000002E-2</v>
-      </c>
-      <c r="Q13" s="78">
+      <c r="P13" s="88">
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="Q13" s="88">
         <f t="shared" si="2"/>
-        <v>0.43200000000000005</v>
-      </c>
-      <c r="R13" s="81" t="s">
-        <v>100</v>
-      </c>
-      <c r="S13" s="75"/>
+        <v>0.35799999999999998</v>
+      </c>
+      <c r="R13" s="70" t="s">
+        <v>104</v>
+      </c>
+      <c r="S13" s="84"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
@@ -1949,55 +1972,55 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="74" t="s">
+      <c r="C15" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="75" t="s">
+      <c r="D15" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="76" t="s">
+      <c r="E15" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="75" t="s">
+      <c r="F15" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="76" t="s">
+      <c r="G15" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="75" t="s">
+      <c r="H15" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="I15" s="75" t="s">
+      <c r="I15" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="J15" s="75" t="s">
+      <c r="J15" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="K15" s="76" t="s">
+      <c r="K15" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="L15" s="75">
+      <c r="L15" s="65">
         <v>1</v>
       </c>
-      <c r="M15" s="75">
+      <c r="M15" s="65">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N15" s="75">
+      <c r="N15" s="65">
         <v>50</v>
       </c>
-      <c r="O15" s="77" t="s">
+      <c r="O15" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="P15" s="78">
+      <c r="P15" s="68">
         <v>1.3299999999999999E-2</v>
       </c>
-      <c r="Q15" s="78">
+      <c r="Q15" s="68">
         <f t="shared" si="2"/>
         <v>0.66499999999999992</v>
       </c>
-      <c r="R15" s="79"/>
-      <c r="S15" s="75"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="65"/>
     </row>
     <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
@@ -2061,41 +2084,41 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="74" t="s">
+      <c r="C17" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="75" t="s">
+      <c r="D17" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="76" t="s">
+      <c r="E17" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="75" t="s">
+      <c r="F17" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="G17" s="76" t="s">
+      <c r="G17" s="66" t="s">
         <v>45</v>
       </c>
-      <c r="H17" s="75" t="s">
+      <c r="H17" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="I17" s="75" t="s">
+      <c r="I17" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="J17" s="75" t="s">
+      <c r="J17" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="K17" s="76" t="s">
+      <c r="K17" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="L17" s="75">
+      <c r="L17" s="65">
         <v>5</v>
       </c>
-      <c r="M17" s="75">
+      <c r="M17" s="65">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="N17" s="75">
+      <c r="N17" s="65">
         <v>100</v>
       </c>
       <c r="O17" s="55" t="s">
@@ -2104,12 +2127,12 @@
       <c r="P17" s="56">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q17" s="78">
+      <c r="Q17" s="68">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="R17" s="79"/>
-      <c r="S17" s="75"/>
+      <c r="R17" s="69"/>
+      <c r="S17" s="65"/>
     </row>
     <row r="18" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
@@ -2173,55 +2196,55 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="74" t="s">
+      <c r="C19" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="75" t="s">
+      <c r="D19" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="76" t="s">
+      <c r="E19" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="75" t="s">
+      <c r="F19" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="G19" s="76" t="s">
+      <c r="G19" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="H19" s="75" t="s">
+      <c r="H19" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="I19" s="75" t="s">
+      <c r="I19" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="J19" s="75" t="s">
+      <c r="J19" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="K19" s="76" t="s">
+      <c r="K19" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="L19" s="75">
+      <c r="L19" s="65">
         <v>1</v>
       </c>
-      <c r="M19" s="75">
+      <c r="M19" s="65">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N19" s="75">
+      <c r="N19" s="65">
         <v>6</v>
       </c>
-      <c r="O19" s="77" t="s">
+      <c r="O19" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="P19" s="78">
+      <c r="P19" s="68">
         <v>0.70479999999999998</v>
       </c>
-      <c r="Q19" s="78">
+      <c r="Q19" s="68">
         <f t="shared" si="2"/>
         <v>4.2287999999999997</v>
       </c>
-      <c r="R19" s="79"/>
-      <c r="S19" s="75"/>
+      <c r="R19" s="69"/>
+      <c r="S19" s="65"/>
     </row>
     <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
@@ -2286,7 +2309,7 @@
         <v>12</v>
       </c>
       <c r="C21" s="61" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D21" s="46" t="s">
         <v>80</v>
@@ -2298,16 +2321,16 @@
         <v>79</v>
       </c>
       <c r="G21" s="47" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H21" s="54" t="s">
         <v>80</v>
       </c>
       <c r="I21" s="46" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J21" s="46" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K21" s="47"/>
       <c r="L21" s="54">
@@ -2326,7 +2349,7 @@
       <c r="P21" s="56">
         <v>1.0251999999999999</v>
       </c>
-      <c r="Q21" s="73">
+      <c r="Q21" s="63">
         <f>P21*N21</f>
         <v>5.1259999999999994</v>
       </c>
@@ -2347,17 +2370,17 @@
       <c r="K22" s="37"/>
       <c r="L22" s="37"/>
       <c r="M22" s="37"/>
-      <c r="N22" s="71" t="s">
+      <c r="N22" s="79" t="s">
         <v>92</v>
       </c>
-      <c r="O22" s="72"/>
-      <c r="P22" s="72"/>
+      <c r="O22" s="80"/>
+      <c r="P22" s="80"/>
       <c r="Q22" s="59">
         <f>SUM(Q10:Q21)</f>
-        <v>19.991399999999999</v>
-      </c>
-      <c r="R22" s="67"/>
-      <c r="S22" s="68"/>
+        <v>19.917400000000001</v>
+      </c>
+      <c r="R22" s="75"/>
+      <c r="S22" s="76"/>
     </row>
     <row r="23" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
@@ -2373,17 +2396,17 @@
       <c r="K23" s="10"/>
       <c r="L23" s="10"/>
       <c r="M23" s="10"/>
-      <c r="N23" s="71" t="s">
+      <c r="N23" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="O23" s="72"/>
-      <c r="P23" s="72"/>
+      <c r="O23" s="80"/>
+      <c r="P23" s="80"/>
       <c r="Q23" s="60">
         <f>Q22/5</f>
-        <v>3.9982799999999998</v>
-      </c>
-      <c r="R23" s="69"/>
-      <c r="S23" s="70"/>
+        <v>3.9834800000000001</v>
+      </c>
+      <c r="R23" s="77"/>
+      <c r="S23" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2403,9 +2426,9 @@
     <hyperlink ref="O18" r:id="rId7"/>
     <hyperlink ref="O19" r:id="rId8"/>
     <hyperlink ref="O16" r:id="rId9"/>
-    <hyperlink ref="O13" r:id="rId10"/>
-    <hyperlink ref="O20" r:id="rId11"/>
-    <hyperlink ref="O21" r:id="rId12"/>
+    <hyperlink ref="O20" r:id="rId10"/>
+    <hyperlink ref="O21" r:id="rId11"/>
+    <hyperlink ref="O13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
